--- a/artfynd/A 25588-2023 artfynd.xlsx
+++ b/artfynd/A 25588-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25588-2023 artfynd.xlsx
+++ b/artfynd/A 25588-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1862612</v>
+        <v>1862611</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485582.8181468264</v>
+        <v>485607</v>
       </c>
       <c r="R2" t="n">
-        <v>6651941.600114551</v>
+        <v>6651929</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2012-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-11-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,6 +774,108 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1862612</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lustigberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>485583</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6651942</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2012-01-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2012-11-20</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
